--- a/Excel_detallado/Excel_Calc_Detallado.xlsx
+++ b/Excel_detallado/Excel_Calc_Detallado.xlsx
@@ -5,7 +5,7 @@
   <fileSharing readOnlyRecommended="0" userName="maximo"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="6" xWindow="240" yWindow="60" windowWidth="0" windowHeight="0" tabRatio="500"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="0" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Parámetros" sheetId="1" r:id="rId4"/>
@@ -19,17 +19,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1782402259" val="1234" rev="124" rev64="64" revOS="3" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1782402259" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1782402259" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1782402259"/>
+      <pm:revision xmlns:pm="smNativeData" day="1782566527" val="1234" rev="124" rev64="64" revOS="3" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1782566527" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1782566527" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1782566527"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="188">
   <si>
     <t>PARAMETROS</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Bo (GHz)</t>
   </si>
   <si>
+    <t>Normalizado a 0,1nm</t>
+  </si>
+  <si>
     <t>Multiplexador DCP-R-9D</t>
   </si>
   <si>
@@ -202,13 +205,13 @@
     <t>Justificacion de los valores asignados en C48, C49, C50 y C59</t>
   </si>
   <si>
-    <t>Area efectiva - Ae</t>
-  </si>
-  <si>
-    <t>Indice no lineal - ñ</t>
-  </si>
-  <si>
-    <t>Coeficiente no linealidad - Lambda</t>
+    <t>Area efectiva - Ae [um²]</t>
+  </si>
+  <si>
+    <t>Indice no lineal - ñ [um²/W]</t>
+  </si>
+  <si>
+    <t>Coeficiente no linealidad - Lambda [Wkm^-1]</t>
   </si>
   <si>
     <t>Longitud maxima de 50,4 km/rollo</t>
@@ -275,6 +278,9 @@
   </si>
   <si>
     <t xml:space="preserve">Benavidez - Rosario </t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculos normalizados a 0,1 nm </t>
   </si>
   <si>
     <t>Presupuesto de Potencia</t>
@@ -617,7 +623,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -632,7 +638,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -648,7 +654,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -665,7 +671,7 @@
       <u val="single"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="single" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="single" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -680,7 +686,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -695,7 +701,7 @@
       <sz val="14"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" fgClr="1F497D" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" fgClr="1F497D" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="280" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="280" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="280" lang="default" weight="bold"/>
@@ -710,7 +716,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -725,7 +731,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -739,7 +745,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -755,7 +761,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="200" lang="default" weight="bold"/>
@@ -770,7 +776,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="220" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" i="1"/>
@@ -784,7 +790,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782402259" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782566527" ulstyle="none" kern="1">
             <pm:latin face="&quot;Calibri&quot;" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -793,7 +799,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="54">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -815,7 +821,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="009BBB59" bgLvl="0" bgClr="009BBB59"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="009BBB59" bgLvl="0" bgClr="009BBB59"/>
           </ext>
         </extLst>
       </patternFill>
@@ -826,7 +832,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00C9DAF8" bgLvl="0" bgClr="00C9DAF8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00C9DAF8" bgLvl="0" bgClr="00C9DAF8"/>
           </ext>
         </extLst>
       </patternFill>
@@ -837,7 +843,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00A2C4C9" bgLvl="0" bgClr="00A2C4C9"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00A2C4C9" bgLvl="0" bgClr="00A2C4C9"/>
           </ext>
         </extLst>
       </patternFill>
@@ -848,7 +854,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFD966" bgLvl="0" bgClr="00FFD966"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFD966" bgLvl="0" bgClr="00FFD966"/>
           </ext>
         </extLst>
       </patternFill>
@@ -859,7 +865,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFD966" bgLvl="0" bgClr="00FFD966"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFD966" bgLvl="0" bgClr="00FFD966"/>
           </ext>
         </extLst>
       </patternFill>
@@ -870,7 +876,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00DD7E6B" bgLvl="0" bgClr="00DD7E6B"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00DD7E6B" bgLvl="0" bgClr="00DD7E6B"/>
           </ext>
         </extLst>
       </patternFill>
@@ -881,7 +887,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00A4C2F4" bgLvl="0" bgClr="00A4C2F4"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00A4C2F4" bgLvl="0" bgClr="00A4C2F4"/>
           </ext>
         </extLst>
       </patternFill>
@@ -892,7 +898,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00F3F3F3" bgLvl="0" bgClr="00F3F3F3"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00F3F3F3" bgLvl="0" bgClr="00F3F3F3"/>
           </ext>
         </extLst>
       </patternFill>
@@ -903,7 +909,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
           </ext>
         </extLst>
       </patternFill>
@@ -914,7 +920,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="001F497D" bgLvl="0" bgClr="001F497D"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="001F497D" bgLvl="0" bgClr="001F497D"/>
           </ext>
         </extLst>
       </patternFill>
@@ -925,7 +931,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00DCE6F1"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00DCE6F1"/>
           </ext>
         </extLst>
       </patternFill>
@@ -936,7 +942,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -947,7 +953,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -973,7 +979,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -984,7 +990,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00E4F0E8" bgLvl="0" bgClr="00E4F0E8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00E4F0E8" bgLvl="0" bgClr="00E4F0E8"/>
           </ext>
         </extLst>
       </patternFill>
@@ -995,7 +1001,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00FF0000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00FF0000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1009,7 +1015,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1020,7 +1026,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00FF0000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00FF0000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1031,7 +1037,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00D9D2E9" bgLvl="0" bgClr="00D9D2E9"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1042,7 +1048,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="009EFF9E"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="009EFF9E"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1053,7 +1059,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="009E9EFF" bgLvl="0" bgClr="009E9EFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="009E9EFF" bgLvl="0" bgClr="009E9EFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1064,7 +1070,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00E0E0FF" bgLvl="0" bgClr="00E0E0FF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00E0E0FF" bgLvl="0" bgClr="00E0E0FF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1075,7 +1081,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFE599"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFE599"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1095,7 +1101,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="0000FF00"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="0000FF00"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1106,7 +1112,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFE599"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFE599"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1117,7 +1123,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00B6D7A8" bgLvl="0" bgClr="00B6D7A8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00B6D7A8" bgLvl="0" bgClr="00B6D7A8"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1128,7 +1134,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00A4C2F4" bgLvl="0" bgClr="00A4C2F4"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00A4C2F4" bgLvl="0" bgClr="00A4C2F4"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1139,7 +1145,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00CFE2F3" bgLvl="0" bgClr="00CFE2F3"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00CFE2F3" bgLvl="0" bgClr="00CFE2F3"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1153,7 +1159,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00EA9999" bgLvl="0" bgClr="00EA9999"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00EA9999" bgLvl="0" bgClr="00EA9999"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1163,22 +1169,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9EFF9E"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="009EFF9E" bgLvl="0" bgClr="009EFF9E"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1189,40 +1184,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1D100"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="82" fgClr="00FFFF00" bgLvl="18" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FF0000" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1233,7 +1195,40 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9EFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1244,57 +1239,19 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782566527" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD966"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFD966" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE599"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00FFE599" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0E0FF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782402259" type="1" fgLvl="100" fgClr="00E0E0FF" bgLvl="0" bgClr="00E0E0FF"/>
-          </ext>
-        </extLst>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="53">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -1310,7 +1267,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1329,7 +1286,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1352,7 +1309,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1374,7 +1331,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1397,7 +1354,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1416,7 +1373,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1435,7 +1392,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1454,7 +1411,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1473,7 +1430,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1496,7 +1453,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1515,7 +1472,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1534,7 +1491,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1553,7 +1510,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1572,7 +1529,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1591,7 +1548,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1610,7 +1567,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1633,7 +1590,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1655,7 +1612,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
             <pm:line position="bottom" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
             <pm:line position="left" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
@@ -1678,7 +1635,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
             <pm:line position="bottom" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
             <pm:line position="right" type="1" style="0" width="50" dist="20" width2="20" rgb="93C47D"/>
@@ -1701,7 +1658,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
             <pm:line position="bottom" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
             <pm:line position="left" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
@@ -1724,7 +1681,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
             <pm:line position="bottom" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
           </pm:border>
@@ -1746,7 +1703,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
             <pm:line position="bottom" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
             <pm:line position="right" type="1" style="0" width="50" dist="20" width2="20" rgb="C27BA0"/>
@@ -1769,7 +1726,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -1790,7 +1747,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1809,7 +1766,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -1830,7 +1787,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1852,7 +1809,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -1874,7 +1831,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -1893,7 +1850,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1916,7 +1873,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1940,7 +1897,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1964,7 +1921,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1988,7 +1945,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2007,7 +1964,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="FFE599"/>
           </pm:border>
         </ext>
@@ -2028,7 +1985,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="50" dist="20" width2="20" rgb="FFE599"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -2050,7 +2007,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
         </ext>
@@ -2071,7 +2028,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2090,7 +2047,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2114,7 +2071,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2137,7 +2094,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2161,7 +2118,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2185,7 +2142,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2208,7 +2165,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2227,7 +2184,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2251,45 +2208,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2308,7 +2227,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
           </pm:border>
@@ -2330,7 +2249,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2349,64 +2268,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
         </ext>
       </extLst>
     </border>
@@ -2425,31 +2287,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -2473,7 +2311,70 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782402259"/>
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1782566527"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1782566527">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
         </ext>
       </extLst>
     </border>
@@ -2481,7 +2382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2810,33 +2711,45 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="46" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="44" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="46" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="48" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="44" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="50" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="46" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="51" borderId="50" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="47" borderId="46" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="50" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="46" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="52" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="47" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="52" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="50" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="47" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="46" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="55" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="49" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="54" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="49" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="49" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -2844,10 +2757,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1782402259" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1782566527" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1782402259" count="20">
+      <pm:colors xmlns:pm="smNativeData" id="1782566527" count="22">
         <pm:color name="Color 24" rgb="1F497D"/>
         <pm:color name="Color 25" rgb="9BBB59"/>
         <pm:color name="Color 26" rgb="C9DAF8"/>
@@ -2868,6 +2781,8 @@
         <pm:color name="Color 41" rgb="EA9999"/>
         <pm:color name="Color 42" rgb="93C47D"/>
         <pm:color name="Color 43" rgb="C27BA0"/>
+        <pm:color name="Color 44" rgb="D1D100"/>
+        <pm:color name="Color 45" rgb="FF9EFF"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -2885,7 +2800,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>149225</xdr:colOff>
+      <xdr:colOff>111125</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>36830</xdr:rowOff>
     </xdr:to>
@@ -2895,7 +2810,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAsAAAABgAAADQE5gMxAAAADwAAAMEArABqRAAAuzYAAOIsAAAZBQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAsAAAABgAAADQE5gMxAAAADwAAAMEAgABqRAAAwTYAAOIsAAAZBQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -2908,7 +2823,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11121390" y="8896985"/>
+          <a:off x="11121390" y="8900795"/>
           <a:ext cx="7296150" cy="828675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2946,11 +2861,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="image2.png"/>
+        <xdr:cNvPr id="7" name="image2.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABOAAAABAAAADEAZAFcAAAABwAAAEkCSAMIMwAABl0AAAEeAADfEQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABOAAAABAAAADEAZAFcAAAABwAAAEkCSAMIMwAABl0AAAEeAADfEQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -2996,11 +2911,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image5.png"/>
+        <xdr:cNvPr id="6" name="image5.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA4AAAADgAAAAAAAABXAAAAEQAAAE4AUQIdigAAzkMAAAAeAABUJAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA4AAAADgAAAAAAAABXAAAAEQAAAE4AUQIdigAAzkMAAAAeAABUJAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3046,11 +2961,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image3.png"/>
+        <xdr:cNvPr id="5" name="image3.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABOAAAACAAAADEAOgFTAAAADgAAAAwDAgFkVgAABl0AAFE2AAAIBwAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABOAAAACAAAADEAOgFTAAAADgAAAAwDAgFkVgAABl0AAFE2AAAIBwAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3096,11 +3011,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image8.png"/>
+        <xdr:cNvPr id="4" name="image8.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA4AAAACQAAANICeQJKAAAADQAAAG4BZABqZQAAoEQAAAAeAAA3FAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA4AAAACQAAANICeQJKAAAADQAAAG4BZABqZQAAoEQAAAAeAAA3FAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3146,11 +3061,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image4.png"/>
+        <xdr:cNvPr id="3" name="image4.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABtAGwAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABIAAAACQAAABUEmgBNAAAADQAAAGIB9QP2XwAASFcAABMqAAD7BAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABtAGwAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABIAAAACQAAABUEmgBNAAAADQAAAGIB9QP2XwAASFcAABMqAAD7BAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3181,6 +3096,57 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>245745</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>338455</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>165735</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAC4ADfQHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABWAAAAAgAAACUBnABcAAAABAAAAFAD5gCHGwAAKWcAAF0WAAANCAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4474845" y="16769715"/>
+          <a:ext cx="3635375" cy="1308735"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3205,7 +3171,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAA5Ii8+HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAM8DmgBJAAAADAAAADQCUQHJWQAAI0YAAAAeAADfEQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAA5Ii8+HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAM8DmgBJAAAADAAAADQCUQHJWQAAI0YAAAAeAADfEQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3255,7 +3221,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA6AAAADgAAAAAAAABYAAAAEQAAAJsDUQLwgwAAMkYAAAAeAABUJAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA6AAAADgAAAAAAAABYAAAAEQAAAJsDUQLwgwAAMkYAAAAeAABUJAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3305,7 +3271,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABRAAAACAAAADEAOwFWAAAADgAAAAwDBwFDUAAA3GAAAFI2AAAIBwAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABRAAAACAAAADEAOwFWAAAADgAAAAwDBwFDUAAA3GAAAFI2AAAIBwAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3355,7 +3321,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABRAAAABAAAAPQAegJhAAAACAAAAKsCpQCdMAAAGGEAAAEeAAA3FAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABRAAAABAAAAPQAegJhAAAACAAAAKsCpQCdMAAAGGEAAAEeAAA3FAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3405,7 +3371,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABIAAAACQAAAEkExABNAAAADgAAAOkAJwBDWgAAYFcAABEqAAD7BAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAD/////HgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABIAAAACQAAAEkExABNAAAADgAAAOkAJwBDWgAAYFcAABEqAAD7BAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3456,11 +3422,11 @@
     </xdr:to>
     <xdr:pic macro="">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image6.png"/>
+        <xdr:cNvPr id="4" name="image6.png"/>
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAEAAAABgAAAAAAAAAbAAAADQAAANsCmQJFLwAAgAQAAOQpAACZGwAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAEAAAABgAAAAAAAAAbAAAADQAAANsCmQLhMQAAgAQAAOQpAACZGwAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3473,8 +3439,109 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7684135" y="731520"/>
+          <a:off x="8108315" y="731520"/>
           <a:ext cx="6809740" cy="4486275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>697865</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>153670</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAK8BAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAdAAAABgAAAJ4DkwEhAAAABwAAABMDIwMJNAAAyyIAAJ0HAADBBAAAAAAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8458835" y="5655945"/>
+          <a:ext cx="1237615" cy="772795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605790</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>59690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic macro="">
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen2"/>
+        <xdr:cNvPicPr>
+          <a:extLst>
+            <a:ext uri="smNativeData">
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAlAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAVAAAAAgAAANsCewAmAAAABQAAADIBuQIWEgAAtxgAAAseAABoFAAAAQAAAA=="/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2940050" y="4017645"/>
+          <a:ext cx="4883785" cy="3317240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3515,7 +3582,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAnAAAADgAAAJwBYwJFAAAAEgAAAEYCaADRiQAAEzAAAAAeAADsIgAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAnAAAADgAAAJwBYwJFAAAAEgAAAEYCaADRiQAAEzAAAAAeAADsIgAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3565,7 +3632,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAqAAAACQAAAAMC6QA6AAAADAAAACcADgMjXgAAqzMAAAAeAADfEQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAqAAAACQAAAAMC6QA6AAAADAAAACcADgMjXgAAqzMAAAAeAADfEQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3615,7 +3682,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAKAAmwA9AAAADgAAAFUCZwFuXQAAjEQAABEqAAD7BAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAKAAmwA9AAAADgAAAFUCZwFuXQAAjEQAABEqAAD7BAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3665,7 +3732,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA+AAAACQAAAH4D6QBDAAAADgAAAPgB9AEjXgAA70oAAKkqAACCBQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA+AAAACQAAAH4D6QBDAAAADgAAAPgB9AEjXgAA70oAAKkqAACCBQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3715,7 +3782,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAFUB/wNUAAAADQAAAAwDcgNKZQAAelEAAAAeAAA3FAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAFUB/wNUAAAADQAAAAwDcgNKZQAAelEAAAAeAAA3FAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3770,7 +3837,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAnAAAADgAAAJwBYwJFAAAAEgAAAEYCaADRiQAAEzAAAAAeAADsIgAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAnAAAADgAAAJwBYwJFAAAAEgAAAEYCaADRiQAAEzAAAAAeAADsIgAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3820,7 +3887,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAqAAAACQAAAAMC6QA6AAAADAAAACcADgMjXgAAqzMAAAAeAADfEQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAqAAAACQAAAAMC6QA6AAAADAAAACcADgMjXgAAqzMAAAAeAADfEQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3870,7 +3937,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAKAAmwA9AAAADgAAAFUCZwFuXQAAjEQAABEqAAD7BAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA5AAAACQAAAKAAmwA9AAAADgAAAFUCZwFuXQAAjEQAABEqAAD7BAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3920,7 +3987,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA+AAAACQAAAH4D6QBDAAAADgAAAPgB9AEjXgAA70oAAKkqAACCBQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA+AAAACQAAAH4D6QBDAAAADgAAAPgB9AEjXgAA70oAAKkqAACCBQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -3970,7 +4037,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAFUB/wNUAAAADQAAAAwDcgNKZQAAelEAAAAeAAA3FAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAFUB/wNUAAAADQAAAAwDcgNKZQAAelEAAAAeAAA3FAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4025,7 +4092,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAABAAABHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAuAAAADgAAAGYBCAJMAAAAEQAAANsBzwP7iAAAWTgAAAIeAADsIgAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAABAAABHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAuAAAADgAAAGUBCAJMAAAAEQAAANsBzwP7iAAAWTgAAAIeAADsIgAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4075,7 +4142,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAABAAABHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAwAAAACQAAAAMC6QBAAAAADAAAACcADgMjXgAA1zoAAAAeAADfEQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAABAAABHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAwAAAACQAAAAMC6QBAAAAADAAAACcADgMjXgAA1zoAAAAeAADfEQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4125,7 +4192,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABXAQAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA/AAAACQAAAKAAmwBDAAAADgAAAFUCZwFuXQAAuEsAABEqAAD7BAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABXAQAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAA/AAAACQAAAKAAmwBDAAAADgAAAFUCZwFuXQAAuEsAABEqAAD7BAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4175,7 +4242,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABxCwAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAH4D6QBJAAAADgAAAPgB9AEjXgAAG1IAAKkqAACCBQAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAABxCwAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABEAAAACQAAAH4D6QBJAAAADgAAAPgB9AEjXgAAG1IAAKkqAACCBQAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4225,7 +4292,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_00w9ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABKAAAACQAAAFUB/wNaAAAADQAAAAwDcgNKZQAAplgAAAAeAAA3FAAAAQAAAA=="/>
+              <pm:smNativeData xmlns:pm="smNativeData" val="SMDATA_15_f84/ahMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAABKAAAACQAAAFUB/wNaAAAADQAAAAwDcgNKZQAAplgAAAAeAAA3FAAAAQAAAA=="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -4525,6 +4592,7 @@
     <col min="3" max="3" width="19.252252" customWidth="1"/>
     <col min="4" max="4" width="22.495495" customWidth="1"/>
     <col min="7" max="7" width="14.000000" customWidth="1"/>
+    <col min="8" max="8" width="13.171171" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="13.45">
@@ -4639,12 +4707,12 @@
         <v>23.5</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="2:4" ht="13.45">
+      <c r="F12" s="133"/>
+    </row>
+    <row r="13" spans="2:6" ht="13.45">
       <c r="B13" s="7" t="s">
         <v>17</v>
       </c>
@@ -4652,24 +4720,28 @@
         <v>12.5</v>
       </c>
       <c r="D13" s="6"/>
+      <c r="E13" s="132" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="132"/>
     </row>
     <row r="14" spans="2:4" ht="13.45">
       <c r="B14" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="6"/>
     </row>
     <row r="15" spans="2:8" ht="13.45">
       <c r="B15" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -4677,7 +4749,7 @@
     </row>
     <row r="16" spans="2:4" ht="13.45">
       <c r="B16" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>10</v>
@@ -4686,21 +4758,21 @@
     </row>
     <row r="17" spans="2:4" ht="13.45">
       <c r="B17" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="2:8" ht="13.45">
       <c r="B18" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>-25</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="3"/>
@@ -4710,26 +4782,26 @@
     </row>
     <row r="19" spans="2:10" ht="13.45">
       <c r="B19" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>-41.0200000000000031</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="3"/>
       <c r="I19" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="2:4" ht="13.45">
       <c r="B20" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>21</v>
@@ -4738,7 +4810,7 @@
     </row>
     <row r="21" spans="2:4" ht="13.45">
       <c r="B21" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>20</v>
@@ -4747,20 +4819,20 @@
     </row>
     <row r="22" spans="2:14" ht="13.45">
       <c r="B22" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>-18.0199999999999996</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="3"/>
       <c r="I22" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -4770,7 +4842,7 @@
     </row>
     <row r="23" spans="2:4" ht="13.45">
       <c r="B23" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>5.5</v>
@@ -4779,28 +4851,28 @@
     </row>
     <row r="24" spans="2:4" ht="13.45">
       <c r="B24" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="3"/>
     </row>
     <row r="25" spans="2:7" ht="13.45">
       <c r="B25" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>-25</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="3"/>
     </row>
     <row r="26" spans="2:4" ht="13.45">
       <c r="B26" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>-41.0200000000000031</v>
@@ -4809,7 +4881,7 @@
     </row>
     <row r="27" spans="2:4" ht="13.45">
       <c r="B27" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>21.5</v>
@@ -4818,7 +4890,7 @@
     </row>
     <row r="28" spans="2:4" ht="13.45">
       <c r="B28" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>20</v>
@@ -4827,20 +4899,20 @@
     </row>
     <row r="29" spans="2:14" ht="13.45">
       <c r="B29" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>-17.5199999999999996</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="3"/>
       <c r="I29" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -4850,14 +4922,14 @@
     </row>
     <row r="30" spans="2:9" ht="13.45">
       <c r="B30" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -4869,21 +4941,21 @@
     </row>
     <row r="31" spans="2:4" ht="13.45">
       <c r="B31" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="6"/>
     </row>
     <row r="32" spans="2:4" ht="13.45">
       <c r="B32" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="18"/>
     </row>
     <row r="33" spans="2:4" ht="13.45">
       <c r="B33" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>-28</v>
@@ -4892,7 +4964,7 @@
     </row>
     <row r="34" spans="2:4" ht="13.45">
       <c r="B34" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>-44.0200000000000031</v>
@@ -4901,7 +4973,7 @@
     </row>
     <row r="35" spans="2:4" ht="13.45">
       <c r="B35" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>25</v>
@@ -4910,7 +4982,7 @@
     </row>
     <row r="36" spans="2:4" ht="13.45">
       <c r="B36" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>21.5</v>
@@ -4919,20 +4991,20 @@
     </row>
     <row r="37" spans="2:14" ht="13.45">
       <c r="B37" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>-19.5199999999999996</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="3"/>
       <c r="I37" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -4942,7 +5014,7 @@
     </row>
     <row r="38" spans="2:4" ht="13.45">
       <c r="B38" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>5.5</v>
@@ -4951,14 +5023,14 @@
     </row>
     <row r="39" spans="2:4" ht="13.45">
       <c r="B39" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
     </row>
     <row r="40" spans="2:4" ht="13.45">
       <c r="B40" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" s="22" t="n">
         <v>0.179999999999999964</v>
@@ -4967,7 +5039,7 @@
     </row>
     <row r="41" spans="2:4" ht="13.45">
       <c r="B41" s="22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" s="22" t="n">
         <v>0.185</v>
@@ -4976,7 +5048,7 @@
     </row>
     <row r="42" spans="2:4" ht="13.45">
       <c r="B42" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C42" s="22" t="n">
         <v>18</v>
@@ -4985,7 +5057,7 @@
     </row>
     <row r="43" spans="2:4" ht="13.45">
       <c r="B43" s="22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C43" s="22" t="n">
         <v>0.1</v>
@@ -4994,25 +5066,25 @@
     </row>
     <row r="44" spans="2:4" ht="13.45">
       <c r="B44" s="22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C44" s="22" t="n">
         <v>1304</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="2:11" ht="13.45">
       <c r="B45" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C45" s="22" t="n">
         <v>0.0929999999999999893</v>
       </c>
       <c r="D45" s="21"/>
       <c r="H45" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -5020,7 +5092,7 @@
     </row>
     <row r="46" spans="2:4" ht="13.45">
       <c r="B46" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="22" t="n">
         <v>85</v>
@@ -5029,7 +5101,7 @@
     </row>
     <row r="47" spans="2:4" ht="13.45">
       <c r="B47" s="22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C47" s="22">
         <f>1.8*10^-8</f>
@@ -5039,39 +5111,39 @@
     </row>
     <row r="48" spans="2:7" ht="13.45">
       <c r="B48" s="22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C48" s="22" t="n">
         <v>0.859999999999999787</v>
       </c>
       <c r="D48" s="21"/>
       <c r="E48" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="3"/>
     </row>
     <row r="49" spans="2:4" ht="13.45">
       <c r="B49" s="23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
     </row>
     <row r="50" spans="2:4" ht="13.45">
       <c r="B50" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>20</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:4" ht="13.45">
       <c r="B51" s="25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>-340</v>
@@ -5080,7 +5152,7 @@
     </row>
     <row r="52" spans="2:4" ht="13.45">
       <c r="B52" s="25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C52" s="25" t="n">
         <v>-17</v>
@@ -5089,7 +5161,7 @@
     </row>
     <row r="53" spans="2:4" ht="13.45">
       <c r="B53" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" s="25" t="n">
         <v>2.9</v>
@@ -5098,7 +5170,7 @@
     </row>
     <row r="54" spans="2:4" ht="13.45">
       <c r="B54" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C54" s="25" t="n">
         <v>0.6</v>
@@ -5107,14 +5179,14 @@
     </row>
     <row r="55" spans="2:4" ht="13.45">
       <c r="B55" s="26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
     </row>
     <row r="56" spans="2:4" ht="13.45">
       <c r="B56" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C56" s="28" t="n">
         <v>1</v>
@@ -5123,7 +5195,7 @@
     </row>
     <row r="57" spans="2:4" ht="13.45">
       <c r="B57" s="28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C57" s="28" t="n">
         <v>0.859999999999999787</v>
@@ -5132,7 +5204,7 @@
     </row>
     <row r="58" spans="2:4" ht="13.45">
       <c r="B58" s="28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="28">
         <f>-(1550^2)*C42/(2*PI()*300000)</f>
@@ -5142,7 +5214,7 @@
     </row>
     <row r="59" spans="2:4" ht="13.45">
       <c r="B59" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C59" s="28" t="n">
         <v>40</v>
@@ -5151,7 +5223,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.45">
       <c r="B60" s="28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C60" s="28">
         <f>63.1*10^9</f>
@@ -5159,13 +5231,13 @@
       </c>
       <c r="D60" s="27"/>
       <c r="E60" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" spans="2:4" ht="13.45">
       <c r="B61" s="28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C61" s="28">
         <f>12.5*10^9</f>
@@ -5175,7 +5247,7 @@
     </row>
     <row r="63" spans="2:4" ht="13.45">
       <c r="B63" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>2</v>
@@ -5213,7 +5285,7 @@
     </row>
     <row r="67" spans="2:4" ht="13.45">
       <c r="B67" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>-20</v>
@@ -5276,7 +5348,7 @@
     </row>
     <row r="74" spans="2:3" ht="13.45">
       <c r="B74" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C74">
         <f>31.6*10^9</f>
@@ -5284,8 +5356,8 @@
       </c>
     </row>
     <row r="76" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B76" s="4" t="s">
-        <v>79</v>
+      <c r="B76" s="129" t="s">
+        <v>80</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>2</v>
@@ -5295,7 +5367,7 @@
       </c>
     </row>
     <row r="77" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="130" t="s">
         <v>4</v>
       </c>
       <c r="C77" s="8" t="n">
@@ -5304,7 +5376,7 @@
       <c r="D77" s="6"/>
     </row>
     <row r="78" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="130" t="s">
         <v>5</v>
       </c>
       <c r="C78" s="8" t="n">
@@ -5313,7 +5385,7 @@
       <c r="D78" s="6"/>
     </row>
     <row r="79" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="130" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="8" t="n">
@@ -5322,8 +5394,8 @@
       <c r="D79" s="6"/>
     </row>
     <row r="80" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B80" s="7" t="s">
-        <v>80</v>
+      <c r="B80" s="130" t="s">
+        <v>81</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>-16</v>
@@ -5331,7 +5403,7 @@
       <c r="D80" s="6"/>
     </row>
     <row r="81" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="130" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="8" t="n">
@@ -5340,7 +5412,7 @@
       <c r="D81" s="6"/>
     </row>
     <row r="82" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="130" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="8" t="n">
@@ -5349,7 +5421,7 @@
       <c r="D82" s="6"/>
     </row>
     <row r="83" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="130" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="8" t="n">
@@ -5358,7 +5430,7 @@
       <c r="D83" s="6"/>
     </row>
     <row r="84" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="130" t="s">
         <v>13</v>
       </c>
       <c r="C84" s="8" t="n">
@@ -5367,7 +5439,7 @@
       <c r="D84" s="6"/>
     </row>
     <row r="85" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="130" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="8" t="n">
@@ -5376,7 +5448,7 @@
       <c r="D85" s="6"/>
     </row>
     <row r="86" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="130" t="s">
         <v>17</v>
       </c>
       <c r="C86" s="8" t="n">
@@ -5386,7 +5458,7 @@
     </row>
     <row r="87" spans="2:3" ht="15.75" customHeight="1">
       <c r="B87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C87">
         <f>31.6*10^9</f>
@@ -5421,7 +5493,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -5430,15 +5502,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -5475,9 +5547,11 @@
   <sheetData>
     <row r="1" spans="1:17" ht="13.45">
       <c r="A1" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="30"/>
+        <v>82</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
       <c r="G1" s="30"/>
@@ -5494,60 +5568,60 @@
     </row>
     <row r="2" spans="1:17" ht="13.45">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="13.45">
       <c r="A3" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -5570,7 +5644,7 @@
     </row>
     <row r="4" spans="1:17" ht="13.45">
       <c r="A4" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -5598,25 +5672,25 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" ht="13.45">
       <c r="A5" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -5646,7 +5720,7 @@
     </row>
     <row r="6" spans="1:17" ht="13.45">
       <c r="A6" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -5706,7 +5780,7 @@
     </row>
     <row r="7" spans="1:17" ht="13.45">
       <c r="A7" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -5732,7 +5806,7 @@
     </row>
     <row r="8" spans="1:17" ht="13.45">
       <c r="A8" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="54" t="n">
         <v>80</v>
@@ -5767,7 +5841,7 @@
     </row>
     <row r="9" spans="1:17" ht="13.45">
       <c r="A9" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -5788,7 +5862,7 @@
     </row>
     <row r="10" spans="1:17" ht="13.45">
       <c r="A10" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -5818,7 +5892,7 @@
     </row>
     <row r="11" spans="1:17" ht="13.45">
       <c r="A11" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -5852,28 +5926,28 @@
         <v>908.153257721671025</v>
       </c>
       <c r="L11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q11" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="44">
         <f>10*LOG10(HARMEAN(K11,P6)/2)</f>
         <v>29.3924152546469983</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="13.45">
       <c r="A12" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -5900,7 +5974,7 @@
     </row>
     <row r="13" spans="1:17" ht="13.45">
       <c r="A13" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -5930,7 +6004,7 @@
     </row>
     <row r="14" spans="1:17" ht="13.45">
       <c r="A14" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -5990,7 +6064,7 @@
     </row>
     <row r="15" spans="1:17" ht="13.45">
       <c r="A15" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -6017,7 +6091,7 @@
     </row>
     <row r="16" spans="1:17" ht="13.45">
       <c r="A16" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>13</v>
@@ -6052,7 +6126,7 @@
     </row>
     <row r="17" spans="1:17" ht="13.45">
       <c r="A17" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -6073,7 +6147,7 @@
     </row>
     <row r="18" spans="1:17" ht="13.45">
       <c r="A18" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -6103,7 +6177,7 @@
     </row>
     <row r="19" spans="1:17" ht="13.45">
       <c r="A19" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -6137,28 +6211,28 @@
         <v>520.604559706988994</v>
       </c>
       <c r="L19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P19" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q19" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q19" s="44">
         <f>10*LOG10(HARMEAN(K19,P14)/2)</f>
         <v>27.0120686633635998</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="13.45">
       <c r="A20" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -6185,7 +6259,7 @@
     </row>
     <row r="21" spans="1:17" ht="13.45">
       <c r="A21" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -6215,7 +6289,7 @@
     </row>
     <row r="22" spans="1:17" ht="13.45">
       <c r="A22" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -6275,7 +6349,7 @@
     </row>
     <row r="23" spans="1:17" ht="13.45">
       <c r="A23" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -6302,7 +6376,7 @@
     </row>
     <row r="24" spans="1:17" ht="13.45">
       <c r="A24" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="54" t="n">
         <v>67</v>
@@ -6337,7 +6411,7 @@
     </row>
     <row r="25" spans="1:17" ht="13.45">
       <c r="A25" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -6358,7 +6432,7 @@
     </row>
     <row r="26" spans="1:17" ht="13.45">
       <c r="A26" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -6388,7 +6462,7 @@
     </row>
     <row r="27" spans="1:17" ht="13.45">
       <c r="A27" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -6422,28 +6496,28 @@
         <v>364.890031067344978</v>
       </c>
       <c r="L27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P27" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q27" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q27" s="44">
         <f>10*LOG10(HARMEAN(K27,P22)/2)</f>
         <v>25.4407484200394016</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="13.45">
       <c r="A28" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -6470,7 +6544,7 @@
     </row>
     <row r="29" spans="1:17" ht="13.45">
       <c r="A29" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -6500,7 +6574,7 @@
     </row>
     <row r="30" spans="1:17" ht="13.45">
       <c r="A30" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -6560,7 +6634,7 @@
     </row>
     <row r="31" spans="1:17" ht="13.45">
       <c r="A31" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -6587,7 +6661,7 @@
     </row>
     <row r="32" spans="1:17" ht="13.45">
       <c r="A32" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" s="54" t="n">
         <v>34</v>
@@ -6622,7 +6696,7 @@
     </row>
     <row r="33" spans="1:17" ht="13.45">
       <c r="A33" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -6643,7 +6717,7 @@
     </row>
     <row r="34" spans="1:17" ht="13.45">
       <c r="A34" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -6673,7 +6747,7 @@
     </row>
     <row r="35" spans="1:17" ht="13.45">
       <c r="A35" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -6707,28 +6781,28 @@
         <v>280.878386014033993</v>
       </c>
       <c r="L35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q35" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q35" s="44">
         <f>10*LOG10(HARMEAN(K35,P30)/2)</f>
         <v>24.3007359718899991</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="13.45">
       <c r="A36" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -6755,7 +6829,7 @@
     </row>
     <row r="37" spans="1:17" ht="13.45">
       <c r="A37" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -6785,7 +6859,7 @@
     </row>
     <row r="38" spans="1:17" ht="13.45">
       <c r="A38" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B38" s="30"/>
       <c r="C38" s="30"/>
@@ -6845,7 +6919,7 @@
     </row>
     <row r="39" spans="1:17" ht="13.45">
       <c r="A39" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
@@ -6872,7 +6946,7 @@
     </row>
     <row r="40" spans="1:17" ht="13.45">
       <c r="A40" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B40" s="54" t="n">
         <v>76</v>
@@ -6907,7 +6981,7 @@
     </row>
     <row r="41" spans="1:17" ht="13.45">
       <c r="A41" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -6928,7 +7002,7 @@
     </row>
     <row r="42" spans="1:17" ht="13.45">
       <c r="A42" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -6958,7 +7032,7 @@
     </row>
     <row r="43" spans="1:17" ht="13.45">
       <c r="A43" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -6992,28 +7066,28 @@
         <v>228.312186054878993</v>
       </c>
       <c r="L43" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M43" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N43" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O43" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P43" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q43" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q43" s="44">
         <f>10*LOG10(HARMEAN(K43,P38)/2)</f>
         <v>23.3979438504589012</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="13.45">
       <c r="A44" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
@@ -7040,7 +7114,7 @@
     </row>
     <row r="45" spans="1:17" ht="13.45">
       <c r="A45" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
@@ -7070,7 +7144,7 @@
     </row>
     <row r="46" spans="1:19" ht="13.45">
       <c r="A46" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -7128,13 +7202,13 @@
         <v>23.0011614527466008</v>
       </c>
       <c r="R46" s="62" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S46" s="63"/>
     </row>
     <row r="47" spans="1:17" ht="13.45">
       <c r="A47" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B47" s="30"/>
       <c r="C47" s="30"/>
@@ -7161,7 +7235,7 @@
     </row>
     <row r="48" spans="1:17" ht="13.45">
       <c r="A48" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B48" s="54" t="n">
         <v>81</v>
@@ -7196,7 +7270,7 @@
     </row>
     <row r="49" spans="1:17" ht="13.45">
       <c r="A49" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B49" s="34"/>
       <c r="C49" s="34"/>
@@ -7217,7 +7291,7 @@
     </row>
     <row r="50" spans="1:17" ht="13.45">
       <c r="A50" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
@@ -7247,7 +7321,7 @@
     </row>
     <row r="51" spans="1:17" ht="13.45">
       <c r="A51" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
@@ -7281,28 +7355,28 @@
         <v>192.319686760746009</v>
       </c>
       <c r="L51" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M51" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N51" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O51" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P51" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q51" s="51">
+        <v>103</v>
+      </c>
+      <c r="Q51" s="44">
         <f>10*LOG10(HARMEAN(K51,P46)/2)</f>
         <v>22.6408561442941014</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="13.45">
       <c r="A52" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
@@ -7329,7 +7403,7 @@
     </row>
     <row r="53" spans="1:17" ht="13.45">
       <c r="A53" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
@@ -7361,7 +7435,7 @@
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
       <c r="F54" s="66" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G54" s="67"/>
       <c r="H54" s="67"/>
@@ -7390,7 +7464,7 @@
         <v>22.6408561442941014</v>
       </c>
       <c r="R54" s="71" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="13.45">
@@ -7400,7 +7474,7 @@
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
       <c r="F55" s="66" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H55" s="67"/>
       <c r="I55" s="67"/>
@@ -7424,30 +7498,30 @@
     </row>
     <row r="57" spans="1:9" ht="13.45">
       <c r="A57" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B57" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C57" s="74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D57" s="74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
       <c r="G57" s="75"/>
       <c r="H57" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I57" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="13.45">
       <c r="A58" s="76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B58" s="77" t="n">
         <v>18</v>
@@ -7462,7 +7536,7 @@
       <c r="F58" s="30"/>
       <c r="G58" s="75"/>
       <c r="H58" s="77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I58" s="77" t="n">
         <v>17.0899999999999999</v>
@@ -7470,32 +7544,32 @@
     </row>
     <row r="59" spans="1:9" ht="13.45">
       <c r="A59" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B59" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C59" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D59" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
       <c r="G59" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H59" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I59" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="13.45">
       <c r="A60" s="79" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B60" s="80" t="n">
         <v>80</v>
@@ -7524,7 +7598,7 @@
     </row>
     <row r="61" spans="1:9" ht="13.45">
       <c r="A61" s="79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B61" s="80" t="n">
         <v>13</v>
@@ -7553,7 +7627,7 @@
     </row>
     <row r="62" spans="1:9" ht="13.45">
       <c r="A62" s="79" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B62" s="80" t="n">
         <v>67</v>
@@ -7582,7 +7656,7 @@
     </row>
     <row r="63" spans="1:9" ht="13.45">
       <c r="A63" s="79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B63" s="80" t="n">
         <v>34</v>
@@ -7611,7 +7685,7 @@
     </row>
     <row r="64" spans="1:9" ht="13.45">
       <c r="A64" s="79" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B64" s="80" t="n">
         <v>76</v>
@@ -7640,7 +7714,7 @@
     </row>
     <row r="65" spans="1:9" ht="13.45">
       <c r="A65" s="79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B65" s="80" t="n">
         <v>81</v>
@@ -7698,29 +7772,29 @@
       <c r="F68" s="30"/>
       <c r="G68" s="75"/>
       <c r="H68" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I68" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="13.45">
       <c r="A69" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B69" s="77">
         <f>Parámetros!C43</f>
         <v>0.1</v>
       </c>
       <c r="C69" s="81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D69" s="30"/>
       <c r="E69" s="30"/>
       <c r="F69" s="30"/>
       <c r="G69" s="75"/>
       <c r="H69" s="77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I69" s="77" t="n">
         <v>18.8500000000000014</v>
@@ -7728,30 +7802,30 @@
     </row>
     <row r="70" spans="1:9" ht="13.45">
       <c r="A70" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B70" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C70" s="78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D70" s="30"/>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
       <c r="G70" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H70" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I70" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.45">
       <c r="A71" s="79" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B71" s="80" t="n">
         <v>80</v>
@@ -7777,7 +7851,7 @@
     </row>
     <row r="72" spans="1:9" ht="13.45">
       <c r="A72" s="79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B72" s="80" t="n">
         <v>13</v>
@@ -7803,7 +7877,7 @@
     </row>
     <row r="73" spans="1:9" ht="13.45">
       <c r="A73" s="79" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B73" s="80" t="n">
         <v>67</v>
@@ -7829,7 +7903,7 @@
     </row>
     <row r="74" spans="1:9" ht="13.45">
       <c r="A74" s="79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B74" s="80" t="n">
         <v>34</v>
@@ -7855,7 +7929,7 @@
     </row>
     <row r="75" spans="1:9" ht="13.45">
       <c r="A75" s="79" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B75" s="80" t="n">
         <v>76</v>
@@ -7881,7 +7955,7 @@
     </row>
     <row r="76" spans="1:9" ht="13.45">
       <c r="A76" s="79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B76" s="80" t="n">
         <v>81</v>
@@ -7907,7 +7981,7 @@
     </row>
     <row r="77" spans="1:9" ht="13.45">
       <c r="A77" s="83" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B77" s="82"/>
       <c r="C77" s="84">
@@ -7923,7 +7997,7 @@
     </row>
     <row r="78" spans="2:3" ht="13.45">
       <c r="B78" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C78" s="3"/>
     </row>
@@ -7938,7 +8012,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -7947,15 +8021,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -7992,9 +8066,11 @@
   <sheetData>
     <row r="1" spans="1:17" ht="13.45">
       <c r="A1" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="30"/>
+        <v>144</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
       <c r="G1" s="30"/>
@@ -8011,60 +8087,60 @@
     </row>
     <row r="2" spans="1:17" ht="13.45">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="13.45">
       <c r="A3" s="33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -8087,7 +8163,7 @@
     </row>
     <row r="4" spans="1:17" ht="13.45">
       <c r="A4" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -8115,25 +8191,25 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="41"/>
     </row>
     <row r="5" spans="1:17" ht="13.45">
       <c r="A5" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -8163,7 +8239,7 @@
     </row>
     <row r="6" spans="1:17" ht="13.45">
       <c r="A6" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -8223,7 +8299,7 @@
     </row>
     <row r="7" spans="1:17" ht="13.45">
       <c r="A7" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -8249,7 +8325,7 @@
     </row>
     <row r="8" spans="1:17" ht="13.45">
       <c r="A8" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="54" t="n">
         <v>80</v>
@@ -8284,7 +8360,7 @@
     </row>
     <row r="9" spans="1:17" ht="13.45">
       <c r="A9" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -8305,7 +8381,7 @@
     </row>
     <row r="10" spans="1:17" ht="13.45">
       <c r="A10" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -8335,7 +8411,7 @@
     </row>
     <row r="11" spans="1:17" ht="13.45">
       <c r="A11" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -8369,19 +8445,19 @@
         <v>908.153257721671025</v>
       </c>
       <c r="L11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q11" s="44">
         <f>10*LOG10(HARMEAN(K11,P6)/2)</f>
@@ -8390,7 +8466,7 @@
     </row>
     <row r="12" spans="1:17" ht="13.45">
       <c r="A12" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -8417,7 +8493,7 @@
     </row>
     <row r="13" spans="1:17" ht="13.45">
       <c r="A13" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -8447,7 +8523,7 @@
     </row>
     <row r="14" spans="1:17" ht="13.45">
       <c r="A14" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -8507,7 +8583,7 @@
     </row>
     <row r="15" spans="1:17" ht="13.45">
       <c r="A15" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -8534,7 +8610,7 @@
     </row>
     <row r="16" spans="1:17" ht="13.45">
       <c r="A16" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>13</v>
@@ -8569,7 +8645,7 @@
     </row>
     <row r="17" spans="1:17" ht="13.45">
       <c r="A17" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -8590,7 +8666,7 @@
     </row>
     <row r="18" spans="1:17" ht="13.45">
       <c r="A18" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -8620,7 +8696,7 @@
     </row>
     <row r="19" spans="1:17" ht="13.45">
       <c r="A19" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -8654,19 +8730,19 @@
         <v>520.604559706988994</v>
       </c>
       <c r="L19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P19" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q19" s="44">
         <f>10*LOG10(HARMEAN(K19,P14)/2)</f>
@@ -8675,7 +8751,7 @@
     </row>
     <row r="20" spans="1:17" ht="13.45">
       <c r="A20" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -8702,7 +8778,7 @@
     </row>
     <row r="21" spans="1:17" ht="13.45">
       <c r="A21" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -8732,7 +8808,7 @@
     </row>
     <row r="22" spans="1:17" ht="13.45">
       <c r="A22" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -8792,7 +8868,7 @@
     </row>
     <row r="23" spans="1:17" ht="13.45">
       <c r="A23" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -8819,7 +8895,7 @@
     </row>
     <row r="24" spans="1:17" ht="13.45">
       <c r="A24" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="54" t="n">
         <v>67</v>
@@ -8854,7 +8930,7 @@
     </row>
     <row r="25" spans="1:17" ht="13.45">
       <c r="A25" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
@@ -8875,7 +8951,7 @@
     </row>
     <row r="26" spans="1:17" ht="13.45">
       <c r="A26" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -8905,7 +8981,7 @@
     </row>
     <row r="27" spans="1:17" ht="13.45">
       <c r="A27" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -8939,19 +9015,19 @@
         <v>364.890031067344978</v>
       </c>
       <c r="L27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P27" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="44">
         <f>10*LOG10(HARMEAN(K27,P22)/2)</f>
@@ -8960,7 +9036,7 @@
     </row>
     <row r="28" spans="1:17" ht="13.45">
       <c r="A28" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -8987,7 +9063,7 @@
     </row>
     <row r="29" spans="1:17" ht="13.45">
       <c r="A29" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -9017,7 +9093,7 @@
     </row>
     <row r="30" spans="1:17" ht="13.45">
       <c r="A30" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -9077,7 +9153,7 @@
     </row>
     <row r="31" spans="1:17" ht="13.45">
       <c r="A31" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -9104,7 +9180,7 @@
     </row>
     <row r="32" spans="1:17" ht="13.45">
       <c r="A32" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" s="54" t="n">
         <v>34</v>
@@ -9139,7 +9215,7 @@
     </row>
     <row r="33" spans="1:17" ht="13.45">
       <c r="A33" s="86" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B33" s="87"/>
       <c r="C33" s="87"/>
@@ -9160,7 +9236,7 @@
     </row>
     <row r="34" spans="1:17" ht="13.45">
       <c r="A34" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -9190,7 +9266,7 @@
     </row>
     <row r="35" spans="1:17" ht="13.45">
       <c r="A35" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -9224,19 +9300,19 @@
         <v>280.878386014033993</v>
       </c>
       <c r="L35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q35" s="44">
         <f>10*LOG10(HARMEAN(K35,P30)/2)</f>
@@ -9245,7 +9321,7 @@
     </row>
     <row r="36" spans="1:17" ht="13.45">
       <c r="A36" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -9272,7 +9348,7 @@
     </row>
     <row r="37" spans="1:17" ht="13.45">
       <c r="A37" s="37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -9296,7 +9372,7 @@
     </row>
     <row r="38" spans="1:17" ht="13.45">
       <c r="A38" s="89" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B38" s="90"/>
       <c r="C38" s="90"/>
@@ -9324,25 +9400,25 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L38" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M38" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N38" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O38" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P38" s="96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q38" s="51"/>
     </row>
     <row r="39" spans="1:17" ht="13.45">
       <c r="A39" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
@@ -9372,7 +9448,7 @@
     </row>
     <row r="40" spans="1:17" ht="13.45">
       <c r="A40" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -9432,7 +9508,7 @@
     </row>
     <row r="41" spans="1:17" ht="13.45">
       <c r="A41" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
@@ -9458,7 +9534,7 @@
     </row>
     <row r="42" spans="1:17" ht="13.45">
       <c r="A42" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B42" s="54" t="n">
         <v>76</v>
@@ -9493,7 +9569,7 @@
     </row>
     <row r="43" spans="1:17" ht="13.45">
       <c r="A43" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B43" s="34"/>
       <c r="C43" s="34"/>
@@ -9514,7 +9590,7 @@
     </row>
     <row r="44" spans="1:17" ht="13.45">
       <c r="A44" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
@@ -9544,7 +9620,7 @@
     </row>
     <row r="45" spans="1:17" ht="13.45">
       <c r="A45" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
@@ -9578,19 +9654,19 @@
         <v>908.153257721671025</v>
       </c>
       <c r="L45" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M45" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N45" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O45" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P45" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q45" s="44">
         <f>10*LOG10(HARMEAN(K45,P40)/2)</f>
@@ -9599,7 +9675,7 @@
     </row>
     <row r="46" spans="1:17" ht="13.45">
       <c r="A46" s="37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -9626,7 +9702,7 @@
     </row>
     <row r="47" spans="1:17" ht="13.45">
       <c r="A47" s="37" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B47" s="30"/>
       <c r="C47" s="30"/>
@@ -9656,7 +9732,7 @@
     </row>
     <row r="48" spans="1:17" ht="13.45">
       <c r="A48" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B48" s="30"/>
       <c r="C48" s="30"/>
@@ -9716,7 +9792,7 @@
     </row>
     <row r="49" spans="1:17" ht="13.45">
       <c r="A49" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
@@ -9743,7 +9819,7 @@
     </row>
     <row r="50" spans="1:17" ht="13.45">
       <c r="A50" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B50" s="54" t="n">
         <v>81</v>
@@ -9778,7 +9854,7 @@
     </row>
     <row r="51" spans="1:17" ht="13.45">
       <c r="A51" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B51" s="34"/>
       <c r="C51" s="34"/>
@@ -9799,7 +9875,7 @@
     </row>
     <row r="52" spans="1:17" ht="13.45">
       <c r="A52" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
@@ -9829,7 +9905,7 @@
     </row>
     <row r="53" spans="1:17" ht="13.45">
       <c r="A53" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
@@ -9863,19 +9939,19 @@
         <v>520.604559706988994</v>
       </c>
       <c r="L53" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M53" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N53" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O53" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P53" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q53" s="44">
         <f>10*LOG10(HARMEAN(K53,P48)/2)</f>
@@ -9884,7 +9960,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.45">
       <c r="A54" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
@@ -9911,7 +9987,7 @@
     </row>
     <row r="55" spans="1:17" ht="13.45">
       <c r="A55" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
@@ -9943,7 +10019,7 @@
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
       <c r="F56" s="66" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G56" s="67"/>
       <c r="H56" s="67"/>
@@ -9972,7 +10048,7 @@
         <v>26.9494363070145013</v>
       </c>
       <c r="R56" s="98" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="13.45">
@@ -9982,7 +10058,7 @@
       <c r="D57" s="30"/>
       <c r="E57" s="30"/>
       <c r="F57" s="66" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H57" s="67"/>
       <c r="I57" s="67"/>
@@ -10006,30 +10082,30 @@
     </row>
     <row r="59" spans="1:9" ht="13.45">
       <c r="A59" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B59" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C59" s="74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D59" s="74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
       <c r="G59" s="75"/>
       <c r="H59" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I59" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="13.45">
       <c r="A60" s="76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B60" s="77" t="n">
         <v>18</v>
@@ -10044,7 +10120,7 @@
       <c r="F60" s="30"/>
       <c r="G60" s="75"/>
       <c r="H60" s="77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I60" s="77" t="n">
         <v>17.0899999999999999</v>
@@ -10052,32 +10128,32 @@
     </row>
     <row r="61" spans="1:9" ht="13.45">
       <c r="A61" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C61" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D61" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
       <c r="G61" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H61" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I61" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="13.45">
       <c r="A62" s="79" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B62" s="80" t="n">
         <v>80</v>
@@ -10106,7 +10182,7 @@
     </row>
     <row r="63" spans="1:9" ht="13.45">
       <c r="A63" s="79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B63" s="80" t="n">
         <v>13</v>
@@ -10135,7 +10211,7 @@
     </row>
     <row r="64" spans="1:9" ht="13.45">
       <c r="A64" s="79" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B64" s="80" t="n">
         <v>67</v>
@@ -10164,7 +10240,7 @@
     </row>
     <row r="65" spans="1:9" ht="13.45">
       <c r="A65" s="79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B65" s="80" t="n">
         <v>34</v>
@@ -10193,7 +10269,7 @@
     </row>
     <row r="66" spans="1:9" ht="13.45">
       <c r="A66" s="99" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B66" s="100" t="n">
         <v>76</v>
@@ -10222,7 +10298,7 @@
     </row>
     <row r="67" spans="1:9" ht="13.45">
       <c r="A67" s="79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B67" s="80" t="n">
         <v>81</v>
@@ -10280,29 +10356,29 @@
       <c r="F70" s="30"/>
       <c r="G70" s="75"/>
       <c r="H70" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I70" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="13.45">
       <c r="A71" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B71" s="77">
         <f>Parámetros!C43</f>
         <v>0.1</v>
       </c>
       <c r="C71" s="81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D71" s="30"/>
       <c r="E71" s="30"/>
       <c r="F71" s="30"/>
       <c r="G71" s="75"/>
       <c r="H71" s="77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I71" s="77" t="n">
         <v>18.8500000000000014</v>
@@ -10310,30 +10386,30 @@
     </row>
     <row r="72" spans="1:9" ht="13.45">
       <c r="A72" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B72" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C72" s="78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D72" s="30"/>
       <c r="E72" s="30"/>
       <c r="F72" s="30"/>
       <c r="G72" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H72" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I72" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="13.45">
       <c r="A73" s="79" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B73" s="80" t="n">
         <v>80</v>
@@ -10359,7 +10435,7 @@
     </row>
     <row r="74" spans="1:9" ht="13.45">
       <c r="A74" s="79" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B74" s="80" t="n">
         <v>13</v>
@@ -10385,7 +10461,7 @@
     </row>
     <row r="75" spans="1:9" ht="13.45">
       <c r="A75" s="79" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B75" s="80" t="n">
         <v>67</v>
@@ -10395,7 +10471,7 @@
         <v>0.818535277187244859</v>
       </c>
       <c r="D75" s="84" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E75" s="30"/>
       <c r="F75" s="30"/>
@@ -10413,7 +10489,7 @@
     </row>
     <row r="76" spans="1:9" ht="13.45">
       <c r="A76" s="79" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B76" s="80" t="n">
         <v>34</v>
@@ -10442,7 +10518,7 @@
     </row>
     <row r="77" spans="1:9" ht="13.45">
       <c r="A77" s="99" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B77" s="100" t="n">
         <v>76</v>
@@ -10468,7 +10544,7 @@
     </row>
     <row r="78" spans="1:9" ht="13.45">
       <c r="A78" s="79" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B78" s="80" t="n">
         <v>81</v>
@@ -10494,7 +10570,7 @@
     </row>
     <row r="79" spans="1:9" ht="13.45">
       <c r="A79" s="84" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B79" s="82"/>
       <c r="C79" s="84">
@@ -10510,7 +10586,7 @@
     </row>
     <row r="80" spans="2:9" ht="13.45">
       <c r="B80" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="30"/>
@@ -10530,7 +10606,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10539,15 +10615,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -10564,16 +10640,16 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="11" defaultColWidth="12.630631" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.378378" customWidth="1"/>
-    <col min="2" max="2" width="10.630631" customWidth="1"/>
-    <col min="3" max="3" width="25.252252" customWidth="1"/>
-    <col min="4" max="4" width="16.000000" customWidth="1"/>
-    <col min="5" max="5" width="17.126126" customWidth="1"/>
+    <col min="1" max="1" width="26.873874" customWidth="1"/>
+    <col min="2" max="2" width="11.594595" customWidth="1"/>
+    <col min="3" max="3" width="26.981982" customWidth="1"/>
+    <col min="4" max="4" width="17.855856" customWidth="1"/>
+    <col min="5" max="5" width="19.099099" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.45">
       <c r="A1" s="101" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10582,24 +10658,24 @@
     </row>
     <row r="2" spans="1:5" ht="13.45">
       <c r="A2" s="102" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B2" s="102" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="102" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D2" s="102" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E2" s="102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.45">
       <c r="A3" s="103" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B3" s="103" t="n">
         <v>80</v>
@@ -10617,7 +10693,7 @@
         <v>655.085897887302053</v>
       </c>
       <c r="G3" s="104" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H3" s="105">
         <f>Parámetros!$C$41*LN(10)/10</f>
@@ -10626,7 +10702,7 @@
     </row>
     <row r="4" spans="1:5" ht="13.45">
       <c r="A4" s="103" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B4" s="103" t="n">
         <v>13</v>
@@ -10646,7 +10722,7 @@
     </row>
     <row r="5" spans="1:5" ht="13.45">
       <c r="A5" s="103" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B5" s="103" t="n">
         <v>67</v>
@@ -10666,7 +10742,7 @@
     </row>
     <row r="6" spans="1:5" ht="13.45">
       <c r="A6" s="103" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B6" s="103" t="n">
         <v>34</v>
@@ -10686,7 +10762,7 @@
     </row>
     <row r="7" spans="1:5" ht="13.45">
       <c r="A7" s="103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" s="103" t="n">
         <v>76</v>
@@ -10706,7 +10782,7 @@
     </row>
     <row r="8" spans="1:5" ht="13.45">
       <c r="A8" s="103" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B8" s="103" t="n">
         <v>81</v>
@@ -10726,7 +10802,7 @@
     </row>
     <row r="9" spans="1:2" ht="13.45">
       <c r="A9" s="103" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B9" s="103">
         <f>SUM(B3:B8)</f>
@@ -10735,7 +10811,7 @@
     </row>
     <row r="11" spans="1:5" ht="13.45">
       <c r="A11" s="101" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10744,24 +10820,24 @@
     </row>
     <row r="12" spans="1:5" ht="13.45">
       <c r="A12" s="102" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B12" s="102" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="102" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" s="102" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E12" s="102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="13.45">
       <c r="A13" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" s="103" t="n">
         <v>107</v>
@@ -10781,7 +10857,7 @@
     </row>
     <row r="14" spans="1:5" ht="13.45">
       <c r="A14" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" s="103" t="n">
         <v>95</v>
@@ -10801,7 +10877,7 @@
     </row>
     <row r="15" spans="1:5" ht="13.45">
       <c r="A15" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B15" s="103" t="n">
         <v>77</v>
@@ -10821,7 +10897,7 @@
     </row>
     <row r="16" spans="1:5" ht="13.45">
       <c r="A16" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B16" s="103" t="n">
         <v>74</v>
@@ -10841,7 +10917,7 @@
     </row>
     <row r="17" spans="1:5" ht="13.45">
       <c r="A17" s="103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B17" s="103" t="n">
         <v>96</v>
@@ -10861,7 +10937,7 @@
     </row>
     <row r="18" spans="1:5" ht="13.45">
       <c r="A18" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B18" s="103" t="n">
         <v>64</v>
@@ -10881,7 +10957,7 @@
     </row>
     <row r="19" spans="1:5" ht="13.45">
       <c r="A19" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B19" s="103" t="n">
         <v>79</v>
@@ -10901,7 +10977,7 @@
     </row>
     <row r="20" spans="1:2" ht="13.45">
       <c r="A20" s="103" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B20" s="103">
         <f>SUM(B13:B19)</f>
@@ -10916,7 +10992,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10925,15 +11001,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -10971,11 +11047,13 @@
   <sheetData>
     <row r="1" spans="1:21" ht="13.45">
       <c r="A1" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="D1" s="131" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
       <c r="G1" s="30"/>
@@ -10996,55 +11074,55 @@
     </row>
     <row r="2" spans="1:21" ht="13.45">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R2" s="106"/>
       <c r="S2" s="30"/>
@@ -11053,7 +11131,7 @@
     </row>
     <row r="3" spans="1:21" ht="13.45">
       <c r="A3" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -11080,7 +11158,7 @@
     </row>
     <row r="4" spans="1:21" ht="13.45">
       <c r="A4" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -11108,19 +11186,19 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="108"/>
       <c r="R4" s="30"/>
@@ -11130,7 +11208,7 @@
     </row>
     <row r="5" spans="1:21" ht="13.45">
       <c r="A5" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -11164,7 +11242,7 @@
     </row>
     <row r="6" spans="1:21" ht="13.45">
       <c r="A6" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -11228,7 +11306,7 @@
     </row>
     <row r="7" spans="1:21" ht="13.45">
       <c r="A7" s="37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -11258,7 +11336,7 @@
     </row>
     <row r="8" spans="1:21" ht="13.45">
       <c r="A8" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="54" t="n">
         <v>107</v>
@@ -11297,7 +11375,7 @@
     </row>
     <row r="9" spans="1:21" ht="13.45">
       <c r="A9" s="109" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B9" s="110"/>
       <c r="C9" s="110"/>
@@ -11322,7 +11400,7 @@
     </row>
     <row r="10" spans="1:21" ht="13.45">
       <c r="A10" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -11356,7 +11434,7 @@
     </row>
     <row r="11" spans="1:21" ht="13.45">
       <c r="A11" s="37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -11420,7 +11498,7 @@
     </row>
     <row r="12" spans="1:21" ht="13.45">
       <c r="A12" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="54" t="n">
         <v>95</v>
@@ -11459,7 +11537,7 @@
     </row>
     <row r="13" spans="1:21" ht="13.45">
       <c r="A13" s="109" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" s="110"/>
       <c r="C13" s="110"/>
@@ -11484,7 +11562,7 @@
     </row>
     <row r="14" spans="1:21" ht="13.45">
       <c r="A14" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -11518,7 +11596,7 @@
     </row>
     <row r="15" spans="1:21" ht="13.45">
       <c r="A15" s="37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -11582,7 +11660,7 @@
     </row>
     <row r="16" spans="1:21" ht="13.45">
       <c r="A16" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>77</v>
@@ -11621,7 +11699,7 @@
     </row>
     <row r="17" spans="1:21" ht="13.45">
       <c r="A17" s="109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B17" s="110"/>
       <c r="C17" s="110"/>
@@ -11646,7 +11724,7 @@
     </row>
     <row r="18" spans="1:21" ht="13.45">
       <c r="A18" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -11680,7 +11758,7 @@
     </row>
     <row r="19" spans="1:21" ht="13.45">
       <c r="A19" s="37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -11744,7 +11822,7 @@
     </row>
     <row r="20" spans="1:21" ht="13.45">
       <c r="A20" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" s="54" t="n">
         <v>74</v>
@@ -11783,7 +11861,7 @@
     </row>
     <row r="21" spans="1:21" ht="13.45">
       <c r="A21" s="109" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B21" s="110"/>
       <c r="C21" s="110"/>
@@ -11808,7 +11886,7 @@
     </row>
     <row r="22" spans="1:21" ht="13.45">
       <c r="A22" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -11842,7 +11920,7 @@
     </row>
     <row r="23" spans="1:21" ht="13.45">
       <c r="A23" s="37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -11906,7 +11984,7 @@
     </row>
     <row r="24" spans="1:21" ht="13.45">
       <c r="A24" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="54" t="n">
         <v>96</v>
@@ -11945,7 +12023,7 @@
     </row>
     <row r="25" spans="1:21" ht="13.45">
       <c r="A25" s="109" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B25" s="110"/>
       <c r="C25" s="110"/>
@@ -11970,7 +12048,7 @@
     </row>
     <row r="26" spans="1:21" ht="13.45">
       <c r="A26" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -12004,7 +12082,7 @@
     </row>
     <row r="27" spans="1:21" ht="13.45">
       <c r="A27" s="37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="38">
@@ -12067,7 +12145,7 @@
     </row>
     <row r="28" spans="1:21" ht="13.45">
       <c r="A28" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="54" t="n">
         <v>64</v>
@@ -12106,7 +12184,7 @@
     </row>
     <row r="29" spans="1:21" ht="13.45">
       <c r="A29" s="109" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B29" s="110"/>
       <c r="C29" s="110"/>
@@ -12131,7 +12209,7 @@
     </row>
     <row r="30" spans="1:21" ht="13.45">
       <c r="A30" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -12165,7 +12243,7 @@
     </row>
     <row r="31" spans="1:21" ht="13.45">
       <c r="A31" s="37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -12229,7 +12307,7 @@
     </row>
     <row r="32" spans="1:21" ht="13.45">
       <c r="A32" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" s="54" t="n">
         <v>79</v>
@@ -12268,7 +12346,7 @@
     </row>
     <row r="33" spans="1:21" ht="13.45">
       <c r="A33" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -12293,7 +12371,7 @@
     </row>
     <row r="34" spans="1:21" ht="13.45">
       <c r="A34" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -12327,7 +12405,7 @@
     </row>
     <row r="35" spans="1:21" ht="13.45">
       <c r="A35" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -12361,19 +12439,19 @@
         <v>239.774189633168987</v>
       </c>
       <c r="L35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q35" s="64">
         <f>10*LOG10(HARMEAN(K35,P31)/2)</f>
@@ -12386,7 +12464,7 @@
     </row>
     <row r="36" spans="1:21" ht="13.45">
       <c r="A36" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -12417,7 +12495,7 @@
     </row>
     <row r="37" spans="1:21" ht="13.45">
       <c r="A37" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -12453,7 +12531,7 @@
       <c r="D38" s="30"/>
       <c r="E38" s="30"/>
       <c r="F38" s="66" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G38" s="67"/>
       <c r="H38" s="67"/>
@@ -12482,7 +12560,7 @@
         <v>19.0299391702734013</v>
       </c>
       <c r="R38" s="98" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S38" s="30"/>
       <c r="T38" s="30"/>
@@ -12495,7 +12573,7 @@
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
       <c r="F39" s="66" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H39" s="67"/>
       <c r="I39" s="67"/>
@@ -12545,28 +12623,28 @@
     </row>
     <row r="41" spans="1:9" ht="13.45">
       <c r="A41" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B41" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C41" s="74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D41" s="74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G41" s="75"/>
       <c r="H41" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I41" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="13.45">
       <c r="A42" s="76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B42" s="77" t="n">
         <v>18</v>
@@ -12579,7 +12657,7 @@
       </c>
       <c r="G42" s="75"/>
       <c r="H42" s="77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I42" s="77" t="n">
         <v>17.0899999999999999</v>
@@ -12587,30 +12665,30 @@
     </row>
     <row r="43" spans="1:9" ht="13.45">
       <c r="A43" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B43" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D43" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G43" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H43" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I43" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="13.45">
       <c r="A44" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" s="103" t="n">
         <v>107</v>
@@ -12637,7 +12715,7 @@
     </row>
     <row r="45" spans="1:9" ht="13.45">
       <c r="A45" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B45" s="103" t="n">
         <v>95</v>
@@ -12664,7 +12742,7 @@
     </row>
     <row r="46" spans="1:9" ht="13.45">
       <c r="A46" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B46" s="103" t="n">
         <v>77</v>
@@ -12691,7 +12769,7 @@
     </row>
     <row r="47" spans="1:9" ht="13.45">
       <c r="A47" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B47" s="103" t="n">
         <v>74</v>
@@ -12718,7 +12796,7 @@
     </row>
     <row r="48" spans="1:9" ht="13.45">
       <c r="A48" s="103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B48" s="103" t="n">
         <v>96</v>
@@ -12745,7 +12823,7 @@
     </row>
     <row r="49" spans="1:9" ht="13.45">
       <c r="A49" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B49" s="103" t="n">
         <v>64</v>
@@ -12772,7 +12850,7 @@
     </row>
     <row r="50" spans="1:9" ht="13.45">
       <c r="A50" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B50" s="103" t="n">
         <v>79</v>
@@ -12800,26 +12878,26 @@
     <row r="53" spans="7:9" ht="13.45">
       <c r="G53" s="75"/>
       <c r="H53" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I53" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="13.45">
       <c r="A54" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B54" s="77">
         <f>Parámetros!C43</f>
         <v>0.1</v>
       </c>
       <c r="C54" s="81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G54" s="75"/>
       <c r="H54" s="77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I54" s="77" t="n">
         <v>18.8500000000000014</v>
@@ -12827,27 +12905,27 @@
     </row>
     <row r="55" spans="1:9" ht="13.45">
       <c r="A55" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B55" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G55" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H55" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I55" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="13.45">
       <c r="A56" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B56" s="103" t="n">
         <v>107</v>
@@ -12870,7 +12948,7 @@
     </row>
     <row r="57" spans="1:9" ht="13.45">
       <c r="A57" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B57" s="103" t="n">
         <v>95</v>
@@ -12893,7 +12971,7 @@
     </row>
     <row r="58" spans="1:9" ht="13.45">
       <c r="A58" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B58" s="103" t="n">
         <v>77</v>
@@ -12916,7 +12994,7 @@
     </row>
     <row r="59" spans="1:9" ht="13.45">
       <c r="A59" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B59" s="103" t="n">
         <v>74</v>
@@ -12939,7 +13017,7 @@
     </row>
     <row r="60" spans="1:9" ht="13.45">
       <c r="A60" s="103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B60" s="103" t="n">
         <v>96</v>
@@ -12962,7 +13040,7 @@
     </row>
     <row r="61" spans="1:9" ht="13.45">
       <c r="A61" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B61" s="103" t="n">
         <v>64</v>
@@ -12985,7 +13063,7 @@
     </row>
     <row r="62" spans="1:9" ht="13.45">
       <c r="A62" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B62" s="103" t="n">
         <v>79</v>
@@ -13008,7 +13086,7 @@
     </row>
     <row r="63" spans="1:3" ht="13.45">
       <c r="A63" s="115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B63" s="114"/>
       <c r="C63" s="115">
@@ -13018,7 +13096,7 @@
     </row>
     <row r="64" spans="2:3" ht="13.45">
       <c r="B64" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C64" s="3"/>
     </row>
@@ -13032,7 +13110,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -13041,15 +13119,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -13087,11 +13165,13 @@
   <sheetData>
     <row r="1" spans="1:21" ht="13.45">
       <c r="A1" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="D1" s="131" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
       <c r="G1" s="30"/>
@@ -13112,55 +13192,55 @@
     </row>
     <row r="2" spans="1:21" ht="13.45">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R2" s="106"/>
       <c r="S2" s="30"/>
@@ -13169,7 +13249,7 @@
     </row>
     <row r="3" spans="1:21" ht="13.45">
       <c r="A3" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -13196,7 +13276,7 @@
     </row>
     <row r="4" spans="1:21" ht="13.45">
       <c r="A4" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -13224,19 +13304,19 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="108"/>
       <c r="R4" s="30"/>
@@ -13246,7 +13326,7 @@
     </row>
     <row r="5" spans="1:21" ht="13.45">
       <c r="A5" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -13280,7 +13360,7 @@
     </row>
     <row r="6" spans="1:21" ht="13.45">
       <c r="A6" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -13344,7 +13424,7 @@
     </row>
     <row r="7" spans="1:21" ht="13.45">
       <c r="A7" s="37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -13374,7 +13454,7 @@
     </row>
     <row r="8" spans="1:21" ht="13.45">
       <c r="A8" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="54" t="n">
         <v>107</v>
@@ -13413,7 +13493,7 @@
     </row>
     <row r="9" spans="1:21" ht="13.45">
       <c r="A9" s="109" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B9" s="110"/>
       <c r="C9" s="110"/>
@@ -13438,7 +13518,7 @@
     </row>
     <row r="10" spans="1:21" ht="13.45">
       <c r="A10" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -13472,7 +13552,7 @@
     </row>
     <row r="11" spans="1:21" ht="13.45">
       <c r="A11" s="37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -13536,7 +13616,7 @@
     </row>
     <row r="12" spans="1:21" ht="13.45">
       <c r="A12" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="54" t="n">
         <v>95</v>
@@ -13575,7 +13655,7 @@
     </row>
     <row r="13" spans="1:21" ht="13.45">
       <c r="A13" s="109" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" s="110"/>
       <c r="C13" s="110"/>
@@ -13600,7 +13680,7 @@
     </row>
     <row r="14" spans="1:21" ht="13.45">
       <c r="A14" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -13634,7 +13714,7 @@
     </row>
     <row r="15" spans="1:21" ht="13.45">
       <c r="A15" s="37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -13698,7 +13778,7 @@
     </row>
     <row r="16" spans="1:21" ht="13.45">
       <c r="A16" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>77</v>
@@ -13737,7 +13817,7 @@
     </row>
     <row r="17" spans="1:21" ht="13.45">
       <c r="A17" s="109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B17" s="110"/>
       <c r="C17" s="110"/>
@@ -13762,7 +13842,7 @@
     </row>
     <row r="18" spans="1:21" ht="13.45">
       <c r="A18" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -13796,7 +13876,7 @@
     </row>
     <row r="19" spans="1:21" ht="13.45">
       <c r="A19" s="37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -13860,7 +13940,7 @@
     </row>
     <row r="20" spans="1:21" ht="13.45">
       <c r="A20" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" s="54" t="n">
         <v>74</v>
@@ -13899,7 +13979,7 @@
     </row>
     <row r="21" spans="1:21" ht="13.45">
       <c r="A21" s="109" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B21" s="110"/>
       <c r="C21" s="110"/>
@@ -13924,7 +14004,7 @@
     </row>
     <row r="22" spans="1:21" ht="13.45">
       <c r="A22" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -13958,7 +14038,7 @@
     </row>
     <row r="23" spans="1:21" ht="13.45">
       <c r="A23" s="37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -14022,7 +14102,7 @@
     </row>
     <row r="24" spans="1:21" ht="13.45">
       <c r="A24" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="54" t="n">
         <v>96</v>
@@ -14061,7 +14141,7 @@
     </row>
     <row r="25" spans="1:21" ht="13.45">
       <c r="A25" s="109" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B25" s="110"/>
       <c r="C25" s="110"/>
@@ -14086,7 +14166,7 @@
     </row>
     <row r="26" spans="1:21" ht="13.45">
       <c r="A26" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -14120,7 +14200,7 @@
     </row>
     <row r="27" spans="1:21" ht="13.45">
       <c r="A27" s="37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="38">
@@ -14183,7 +14263,7 @@
     </row>
     <row r="28" spans="1:21" ht="13.45">
       <c r="A28" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="54" t="n">
         <v>64</v>
@@ -14222,7 +14302,7 @@
     </row>
     <row r="29" spans="1:21" ht="13.45">
       <c r="A29" s="109" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B29" s="110"/>
       <c r="C29" s="110"/>
@@ -14247,7 +14327,7 @@
     </row>
     <row r="30" spans="1:21" ht="13.45">
       <c r="A30" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -14281,7 +14361,7 @@
     </row>
     <row r="31" spans="1:21" ht="13.45">
       <c r="A31" s="37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -14345,7 +14425,7 @@
     </row>
     <row r="32" spans="1:21" ht="13.45">
       <c r="A32" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" s="54" t="n">
         <v>79</v>
@@ -14384,7 +14464,7 @@
     </row>
     <row r="33" spans="1:21" ht="13.45">
       <c r="A33" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -14409,7 +14489,7 @@
     </row>
     <row r="34" spans="1:21" ht="13.45">
       <c r="A34" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -14443,7 +14523,7 @@
     </row>
     <row r="35" spans="1:21" ht="13.45">
       <c r="A35" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -14477,19 +14557,19 @@
         <v>239.774189633168987</v>
       </c>
       <c r="L35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q35" s="64">
         <f>10*LOG10(HARMEAN(K35,P31)/2)</f>
@@ -14502,7 +14582,7 @@
     </row>
     <row r="36" spans="1:21" ht="13.45">
       <c r="A36" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -14533,7 +14613,7 @@
     </row>
     <row r="37" spans="1:21" ht="13.45">
       <c r="A37" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -14569,7 +14649,7 @@
       <c r="D38" s="30"/>
       <c r="E38" s="30"/>
       <c r="F38" s="66" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G38" s="67"/>
       <c r="H38" s="67"/>
@@ -14598,7 +14678,7 @@
         <v>19.0299391702734013</v>
       </c>
       <c r="R38" s="118" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="S38" s="30"/>
       <c r="T38" s="30"/>
@@ -14611,7 +14691,7 @@
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
       <c r="F39" s="66" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H39" s="67"/>
       <c r="I39" s="67"/>
@@ -14662,28 +14742,28 @@
     </row>
     <row r="41" spans="1:9" ht="13.45">
       <c r="A41" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B41" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C41" s="74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D41" s="74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G41" s="75"/>
       <c r="H41" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I41" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="13.45">
       <c r="A42" s="76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B42" s="77" t="n">
         <v>18</v>
@@ -14697,7 +14777,7 @@
       </c>
       <c r="G42" s="75"/>
       <c r="H42" s="77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I42" s="77" t="n">
         <v>17.0899999999999999</v>
@@ -14705,30 +14785,30 @@
     </row>
     <row r="43" spans="1:9" ht="13.45">
       <c r="A43" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B43" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C43" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D43" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G43" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H43" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I43" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="13.45">
       <c r="A44" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" s="103" t="n">
         <v>107</v>
@@ -14755,7 +14835,7 @@
     </row>
     <row r="45" spans="1:9" ht="13.45">
       <c r="A45" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B45" s="103" t="n">
         <v>95</v>
@@ -14782,7 +14862,7 @@
     </row>
     <row r="46" spans="1:9" ht="13.45">
       <c r="A46" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B46" s="103" t="n">
         <v>77</v>
@@ -14809,7 +14889,7 @@
     </row>
     <row r="47" spans="1:9" ht="13.45">
       <c r="A47" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B47" s="103" t="n">
         <v>74</v>
@@ -14836,7 +14916,7 @@
     </row>
     <row r="48" spans="1:9" ht="13.45">
       <c r="A48" s="103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B48" s="103" t="n">
         <v>96</v>
@@ -14863,7 +14943,7 @@
     </row>
     <row r="49" spans="1:9" ht="13.45">
       <c r="A49" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B49" s="103" t="n">
         <v>64</v>
@@ -14890,7 +14970,7 @@
     </row>
     <row r="50" spans="1:9" ht="13.45">
       <c r="A50" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B50" s="103" t="n">
         <v>79</v>
@@ -14918,26 +14998,26 @@
     <row r="53" spans="7:9" ht="13.45">
       <c r="G53" s="75"/>
       <c r="H53" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I53" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="13.45">
       <c r="A54" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B54" s="77">
         <f>Parámetros!C43</f>
         <v>0.1</v>
       </c>
       <c r="C54" s="81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G54" s="75"/>
       <c r="H54" s="77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I54" s="77" t="n">
         <v>18.8500000000000014</v>
@@ -14945,27 +15025,27 @@
     </row>
     <row r="55" spans="1:9" ht="13.45">
       <c r="A55" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B55" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G55" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H55" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I55" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="13.45">
       <c r="A56" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B56" s="103" t="n">
         <v>107</v>
@@ -14988,7 +15068,7 @@
     </row>
     <row r="57" spans="1:9" ht="13.45">
       <c r="A57" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B57" s="103" t="n">
         <v>95</v>
@@ -15011,7 +15091,7 @@
     </row>
     <row r="58" spans="1:9" ht="13.45">
       <c r="A58" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B58" s="103" t="n">
         <v>77</v>
@@ -15034,7 +15114,7 @@
     </row>
     <row r="59" spans="1:9" ht="13.45">
       <c r="A59" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B59" s="103" t="n">
         <v>74</v>
@@ -15057,7 +15137,7 @@
     </row>
     <row r="60" spans="1:9" ht="13.45">
       <c r="A60" s="103" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B60" s="103" t="n">
         <v>96</v>
@@ -15080,7 +15160,7 @@
     </row>
     <row r="61" spans="1:9" ht="13.45">
       <c r="A61" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B61" s="103" t="n">
         <v>64</v>
@@ -15103,7 +15183,7 @@
     </row>
     <row r="62" spans="1:9" ht="13.45">
       <c r="A62" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B62" s="103" t="n">
         <v>79</v>
@@ -15126,7 +15206,7 @@
     </row>
     <row r="63" spans="1:3" ht="13.45">
       <c r="A63" s="115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B63" s="114"/>
       <c r="C63" s="115">
@@ -15136,7 +15216,7 @@
     </row>
     <row r="64" spans="2:3" ht="13.45">
       <c r="B64" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C64" s="3"/>
     </row>
@@ -15150,7 +15230,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -15159,15 +15239,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -15205,11 +15285,13 @@
   <sheetData>
     <row r="1" spans="1:21" ht="13.45">
       <c r="A1" s="29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="D1" s="131" t="s">
+        <v>83</v>
+      </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
       <c r="G1" s="30"/>
@@ -15230,55 +15312,55 @@
     </row>
     <row r="2" spans="1:21" ht="13.45">
       <c r="A2" s="32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O2" s="32" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R2" s="106"/>
       <c r="S2" s="30"/>
@@ -15287,7 +15369,7 @@
     </row>
     <row r="3" spans="1:21" ht="13.45">
       <c r="A3" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -15314,7 +15396,7 @@
     </row>
     <row r="4" spans="1:21" ht="13.45">
       <c r="A4" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -15342,19 +15424,19 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P4" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="108"/>
       <c r="R4" s="30"/>
@@ -15364,7 +15446,7 @@
     </row>
     <row r="5" spans="1:21" ht="13.45">
       <c r="A5" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -15398,7 +15480,7 @@
     </row>
     <row r="6" spans="1:21" ht="13.45">
       <c r="A6" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -15462,7 +15544,7 @@
     </row>
     <row r="7" spans="1:21" ht="13.45">
       <c r="A7" s="37" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -15492,7 +15574,7 @@
     </row>
     <row r="8" spans="1:21" ht="13.45">
       <c r="A8" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B8" s="54" t="n">
         <v>107</v>
@@ -15531,7 +15613,7 @@
     </row>
     <row r="9" spans="1:21" ht="13.45">
       <c r="A9" s="109" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B9" s="110"/>
       <c r="C9" s="110"/>
@@ -15556,7 +15638,7 @@
     </row>
     <row r="10" spans="1:21" ht="13.45">
       <c r="A10" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -15590,7 +15672,7 @@
     </row>
     <row r="11" spans="1:21" ht="13.45">
       <c r="A11" s="37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -15654,7 +15736,7 @@
     </row>
     <row r="12" spans="1:21" ht="13.45">
       <c r="A12" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="54" t="n">
         <v>95</v>
@@ -15693,7 +15775,7 @@
     </row>
     <row r="13" spans="1:21" ht="13.45">
       <c r="A13" s="109" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" s="110"/>
       <c r="C13" s="110"/>
@@ -15718,7 +15800,7 @@
     </row>
     <row r="14" spans="1:21" ht="13.45">
       <c r="A14" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -15752,7 +15834,7 @@
     </row>
     <row r="15" spans="1:21" ht="13.45">
       <c r="A15" s="37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -15816,7 +15898,7 @@
     </row>
     <row r="16" spans="1:21" ht="13.45">
       <c r="A16" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>77</v>
@@ -15855,7 +15937,7 @@
     </row>
     <row r="17" spans="1:21" ht="13.45">
       <c r="A17" s="109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B17" s="110"/>
       <c r="C17" s="110"/>
@@ -15880,7 +15962,7 @@
     </row>
     <row r="18" spans="1:21" ht="13.45">
       <c r="A18" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -15914,7 +15996,7 @@
     </row>
     <row r="19" spans="1:21" ht="13.45">
       <c r="A19" s="37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -15978,7 +16060,7 @@
     </row>
     <row r="20" spans="1:21" ht="13.45">
       <c r="A20" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B20" s="54" t="n">
         <v>74</v>
@@ -16017,7 +16099,7 @@
     </row>
     <row r="21" spans="1:21" ht="13.45">
       <c r="A21" s="122" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B21" s="121"/>
       <c r="C21" s="121"/>
@@ -16042,7 +16124,7 @@
     </row>
     <row r="22" spans="1:21" ht="13.45">
       <c r="A22" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -16076,7 +16158,7 @@
     </row>
     <row r="23" spans="1:21" ht="13.45">
       <c r="A23" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -16110,19 +16192,19 @@
         <v>379.382358936881019</v>
       </c>
       <c r="L23" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M23" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N23" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O23" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P23" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q23" s="64">
         <f>10*LOG10(HARMEAN(K22,P19)/2)</f>
@@ -16135,7 +16217,7 @@
     </row>
     <row r="24" spans="1:21" ht="13.45">
       <c r="A24" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
@@ -16166,7 +16248,7 @@
     </row>
     <row r="25" spans="1:21" ht="13.45">
       <c r="A25" s="37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -16194,7 +16276,7 @@
     </row>
     <row r="26" spans="1:21" ht="13.45">
       <c r="A26" s="89" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B26" s="90"/>
       <c r="C26" s="90"/>
@@ -16222,19 +16304,19 @@
         <v>6309.57344480193024</v>
       </c>
       <c r="L26" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M26" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N26" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O26" s="95" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P26" s="96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="64"/>
       <c r="R26" s="30"/>
@@ -16244,7 +16326,7 @@
     </row>
     <row r="27" spans="1:21" ht="13.45">
       <c r="A27" s="37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -16278,7 +16360,7 @@
     </row>
     <row r="28" spans="1:21" ht="13.45">
       <c r="A28" s="37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -16342,7 +16424,7 @@
     </row>
     <row r="29" spans="1:21" ht="13.45">
       <c r="A29" s="37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -16372,7 +16454,7 @@
     </row>
     <row r="30" spans="1:21" ht="13.45">
       <c r="A30" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B30" s="54" t="n">
         <v>96</v>
@@ -16411,7 +16493,7 @@
     </row>
     <row r="31" spans="1:21" ht="13.45">
       <c r="A31" s="109" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B31" s="110"/>
       <c r="C31" s="110"/>
@@ -16436,7 +16518,7 @@
     </row>
     <row r="32" spans="1:21" ht="13.45">
       <c r="A32" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -16470,7 +16552,7 @@
     </row>
     <row r="33" spans="1:21" ht="13.45">
       <c r="A33" s="37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
@@ -16504,28 +16586,28 @@
         <v>1491.49185337579001</v>
       </c>
       <c r="L33" s="47">
-        <f>(2/3)^3*Parámetros!C56*(Parámetros!C57)^2*'No linealidades'!D19*(10^(E33/10)*0.001)^2*LOG10(PI()^2*ABS(Parámetros!C58*10^(-24))*'No linealidades'!D19*(Parámetros!C59)^2*Parámetros!C74^2)/(PI()*ABS(Parámetros!C58*10^(-24))*Parámetros!C74^3)*Parámetros!C73*10^9</f>
-        <v>0.00133267103681900001</v>
+        <f>(2/3)^3*Parámetros!C56*(Parámetros!C57)^2*'No linealidades'!D18*(10^(E33/10)*0.001)^2*LOG10(PI()^2*ABS(Parámetros!C58*10^(-24))*'No linealidades'!D18*(Parámetros!C59)^2*Parámetros!C74^2)/(PI()*ABS(Parámetros!C58*10^(-24))*Parámetros!C74^3)*Parámetros!C73*10^9</f>
+        <v>0.00128534665129500025</v>
       </c>
       <c r="M33" s="48">
         <f>10*LOG10(N33)</f>
-        <v>28.7527704077803996</v>
+        <v>28.9097972957655003</v>
       </c>
       <c r="N33" s="49">
         <f>1/L33</f>
-        <v>750.372726931122997</v>
+        <v>778.000237517630012</v>
       </c>
       <c r="O33" s="48">
         <f>10*LOG10(P33)</f>
-        <v>28.5930154545648989</v>
+        <v>28.7442711283875987</v>
       </c>
       <c r="P33" s="50">
         <f>HARMEAN(N28,N33)/2</f>
-        <v>723.271821567650022</v>
+        <v>748.905659956795034</v>
       </c>
       <c r="Q33" s="64">
         <f>10*LOG10(HARMEAN(K33,P33)/2)</f>
-        <v>26.8759503912291002</v>
+        <v>26.9772291643519999</v>
       </c>
       <c r="R33" s="30"/>
       <c r="S33" s="30"/>
@@ -16534,7 +16616,7 @@
     </row>
     <row r="34" spans="1:21" ht="13.45">
       <c r="A34" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B34" s="54" t="n">
         <v>64</v>
@@ -16573,7 +16655,7 @@
     </row>
     <row r="35" spans="1:21" ht="13.45">
       <c r="A35" s="109" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B35" s="110"/>
       <c r="C35" s="110"/>
@@ -16598,7 +16680,7 @@
     </row>
     <row r="36" spans="1:21" ht="13.45">
       <c r="A36" s="37" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -16632,7 +16714,7 @@
     </row>
     <row r="37" spans="1:21" ht="13.45">
       <c r="A37" s="37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -16666,28 +16748,28 @@
         <v>845.991151182990961</v>
       </c>
       <c r="L37" s="47">
-        <f>(2/3)^3*Parámetros!C56*(Parámetros!C57)^2*'No linealidades'!D18*(10^(E37/10)*0.001)^2*LOG10(PI()^2*ABS(Parámetros!C58*10^(-24))*'No linealidades'!D18*(Parámetros!C59)^2*Parámetros!C74^2)/(PI()*ABS(Parámetros!C58*10^(-24))*Parámetros!C74^3)*Parámetros!C73*10^9</f>
-        <v>0.00128534665129500025</v>
+        <f>(2/3)^3*Parámetros!C56*(Parámetros!C57)^2*'No linealidades'!D19*(10^(E37/10)*0.001)^2*LOG10(PI()^2*ABS(Parámetros!C58*10^(-24))*'No linealidades'!D19*(Parámetros!C59)^2*Parámetros!C74^2)/(PI()*ABS(Parámetros!C58*10^(-24))*Parámetros!C74^3)*Parámetros!C73*10^9</f>
+        <v>0.00133267103681900001</v>
       </c>
       <c r="M37" s="48">
         <f>10*LOG10(N37)</f>
-        <v>28.9097972957655003</v>
+        <v>28.7527704077803996</v>
       </c>
       <c r="N37" s="49">
         <f>1/L37</f>
-        <v>778.000237517630012</v>
+        <v>750.372726931122997</v>
       </c>
       <c r="O37" s="48">
         <f>10*LOG10(P37)</f>
-        <v>26.9833585378307994</v>
+        <v>25.7382187322748983</v>
       </c>
       <c r="P37" s="50">
-        <f>HARMEAN(N28,N32,N37)/3</f>
-        <v>499.270439971196993</v>
+        <f>HARMEAN(N28,N33,N37)/3</f>
+        <v>374.81923783507699</v>
       </c>
       <c r="Q37" s="64">
         <f>10*LOG10(HARMEAN(K37,P37)/2)</f>
-        <v>24.9689493151545001</v>
+        <v>24.1453947725384985</v>
       </c>
       <c r="R37" s="30"/>
       <c r="S37" s="30"/>
@@ -16696,7 +16778,7 @@
     </row>
     <row r="38" spans="1:21" ht="13.45">
       <c r="A38" s="53" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="54" t="n">
         <v>79</v>
@@ -16735,7 +16817,7 @@
     </row>
     <row r="39" spans="1:21" ht="13.45">
       <c r="A39" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -16760,7 +16842,7 @@
     </row>
     <row r="40" spans="1:21" ht="13.45">
       <c r="A40" s="37" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -16794,7 +16876,7 @@
     </row>
     <row r="41" spans="1:21" ht="13.45">
       <c r="A41" s="37" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
@@ -16828,23 +16910,23 @@
         <v>619.016231734761959</v>
       </c>
       <c r="L41" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M41" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N41" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O41" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P41" s="40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q41" s="64">
         <f>10*LOG10(HARMEAN(K41,P37)/2)</f>
-        <v>24.414847421532901</v>
+        <v>23.6820941791696988</v>
       </c>
       <c r="R41" s="30"/>
       <c r="S41" s="30"/>
@@ -16853,7 +16935,7 @@
     </row>
     <row r="42" spans="1:21" ht="13.45">
       <c r="A42" s="37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -16884,7 +16966,7 @@
     </row>
     <row r="43" spans="1:21" ht="13.45">
       <c r="A43" s="37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -16920,7 +17002,7 @@
       <c r="D44" s="30"/>
       <c r="E44" s="30"/>
       <c r="F44" s="66" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G44" s="67"/>
       <c r="H44" s="67"/>
@@ -16938,18 +17020,18 @@
       <c r="N44" s="67"/>
       <c r="O44" s="113">
         <f>O37</f>
-        <v>26.9833585378307994</v>
+        <v>25.7382187322748983</v>
       </c>
       <c r="P44" s="112">
         <f>P37</f>
-        <v>499.270439971196993</v>
+        <v>374.81923783507699</v>
       </c>
       <c r="Q44" s="70">
         <f>10*LOG10(HARMEAN(K44,P44)/2)</f>
-        <v>24.414847421532901</v>
+        <v>23.6820941791696988</v>
       </c>
       <c r="R44" s="124" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S44" s="30"/>
       <c r="T44" s="30"/>
@@ -16962,7 +17044,7 @@
       <c r="D45" s="30"/>
       <c r="E45" s="30"/>
       <c r="F45" s="66" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H45" s="67"/>
       <c r="I45" s="67"/>
@@ -17013,28 +17095,28 @@
     </row>
     <row r="47" spans="1:9" ht="13.45">
       <c r="A47" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B47" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C47" s="74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D47" s="74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G47" s="75"/>
       <c r="H47" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I47" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="13.45">
       <c r="A48" s="76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B48" s="77" t="n">
         <v>18</v>
@@ -17048,7 +17130,7 @@
       </c>
       <c r="G48" s="75"/>
       <c r="H48" s="77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I48" s="77" t="n">
         <v>17.0899999999999999</v>
@@ -17056,30 +17138,30 @@
     </row>
     <row r="49" spans="1:9" ht="13.45">
       <c r="A49" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B49" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D49" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G49" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H49" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I49" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="13.45">
       <c r="A50" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B50" s="103" t="n">
         <v>107</v>
@@ -17106,7 +17188,7 @@
     </row>
     <row r="51" spans="1:9" ht="13.45">
       <c r="A51" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B51" s="103" t="n">
         <v>95</v>
@@ -17133,7 +17215,7 @@
     </row>
     <row r="52" spans="1:9" ht="13.45">
       <c r="A52" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B52" s="103" t="n">
         <v>77</v>
@@ -17160,7 +17242,7 @@
     </row>
     <row r="53" spans="1:9" ht="13.45">
       <c r="A53" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B53" s="103" t="n">
         <v>74</v>
@@ -17187,7 +17269,7 @@
     </row>
     <row r="54" spans="1:9" ht="13.45">
       <c r="A54" s="127" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B54" s="127" t="n">
         <v>96</v>
@@ -17214,7 +17296,7 @@
     </row>
     <row r="55" spans="1:9" ht="13.45">
       <c r="A55" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B55" s="103" t="n">
         <v>64</v>
@@ -17241,7 +17323,7 @@
     </row>
     <row r="56" spans="1:9" ht="13.45">
       <c r="A56" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B56" s="103" t="n">
         <v>79</v>
@@ -17269,26 +17351,26 @@
     <row r="59" spans="7:9" ht="13.45">
       <c r="G59" s="75"/>
       <c r="H59" s="74" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I59" s="74" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="13.45">
       <c r="A60" s="74" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B60" s="77">
         <f>Parámetros!C43</f>
         <v>0.1</v>
       </c>
       <c r="C60" s="81" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G60" s="75"/>
       <c r="H60" s="77" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I60" s="77" t="n">
         <v>18.8500000000000014</v>
@@ -17296,27 +17378,27 @@
     </row>
     <row r="61" spans="1:9" ht="13.45">
       <c r="A61" s="78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C61" s="78" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G61" s="78" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H61" s="78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I61" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="13.45">
       <c r="A62" s="103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B62" s="103" t="n">
         <v>107</v>
@@ -17339,7 +17421,7 @@
     </row>
     <row r="63" spans="1:9" ht="13.45">
       <c r="A63" s="103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B63" s="103" t="n">
         <v>95</v>
@@ -17362,7 +17444,7 @@
     </row>
     <row r="64" spans="1:9" ht="13.45">
       <c r="A64" s="103" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B64" s="103" t="n">
         <v>77</v>
@@ -17385,7 +17467,7 @@
     </row>
     <row r="65" spans="1:9" ht="13.45">
       <c r="A65" s="103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B65" s="103" t="n">
         <v>74</v>
@@ -17408,7 +17490,7 @@
     </row>
     <row r="66" spans="1:9" ht="13.45">
       <c r="A66" s="121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B66" s="126" t="n">
         <v>96</v>
@@ -17431,7 +17513,7 @@
     </row>
     <row r="67" spans="1:9" ht="13.45">
       <c r="A67" s="103" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B67" s="103" t="n">
         <v>64</v>
@@ -17454,7 +17536,7 @@
     </row>
     <row r="68" spans="1:9" ht="13.45">
       <c r="A68" s="103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B68" s="103" t="n">
         <v>79</v>
@@ -17477,7 +17559,7 @@
     </row>
     <row r="69" spans="1:3" ht="13.45">
       <c r="A69" s="115" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B69" s="114"/>
       <c r="C69" s="115">
@@ -17487,7 +17569,7 @@
     </row>
     <row r="70" spans="2:3" ht="13.45">
       <c r="B70" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C70" s="3"/>
     </row>
@@ -17500,7 +17582,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782402259" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782566527" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -17509,15 +17591,15 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782402259" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782566527" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782402259" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782566527" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
